--- a/output/Tables/2019/Resampling/HIA_per_disease.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease.xlsx
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>3564.551</v>
+        <v>3974.078</v>
       </c>
       <c r="C4">
-        <v>2018.217</v>
+        <v>2842.134</v>
       </c>
       <c r="D4">
-        <v>5284.388</v>
+        <v>5104.737</v>
       </c>
       <c r="E4">
-        <v>5635.001</v>
+        <v>6273.717</v>
       </c>
       <c r="F4">
-        <v>3187.033</v>
+        <v>4459.626</v>
       </c>
       <c r="G4">
-        <v>8351.668</v>
+        <v>8094.704</v>
       </c>
       <c r="H4">
-        <v>167498405.189</v>
+        <v>186793574.592</v>
       </c>
       <c r="I4">
-        <v>94722738.27599999</v>
+        <v>133630235.149</v>
       </c>
       <c r="J4">
-        <v>248636995.545</v>
+        <v>240231003.475</v>
       </c>
       <c r="K4">
-        <v>748910514.244</v>
+        <v>834371355.705</v>
       </c>
       <c r="L4">
-        <v>425364386.377</v>
+        <v>593160156.525</v>
       </c>
       <c r="M4">
-        <v>1109811467.017</v>
+        <v>1074735879.446</v>
       </c>
     </row>
     <row r="5">
@@ -695,13 +695,13 @@
         <v>247361.635</v>
       </c>
       <c r="E8">
-        <v>1202511.896</v>
+        <v>200418.649</v>
       </c>
       <c r="F8">
-        <v>784972.6310000001</v>
+        <v>130828.772</v>
       </c>
       <c r="G8">
-        <v>1694593.505</v>
+        <v>282432.251</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>160291832831.95</v>
+        <v>26715305471.992</v>
       </c>
       <c r="L8">
-        <v>104474559281.82</v>
+        <v>17412426546.97</v>
       </c>
       <c r="M8">
-        <v>224739687668.292</v>
+        <v>37456614611.382</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>205237.145</v>
+        <v>205646.672</v>
       </c>
       <c r="C9">
-        <v>126120.824</v>
+        <v>126944.741</v>
       </c>
       <c r="D9">
-        <v>295933.078</v>
+        <v>295753.427</v>
       </c>
       <c r="E9">
-        <v>1232443.803</v>
+        <v>230989.272</v>
       </c>
       <c r="F9">
-        <v>794703.8600000001</v>
+        <v>141832.594</v>
       </c>
       <c r="G9">
-        <v>1746268.926</v>
+        <v>333850.708</v>
       </c>
       <c r="H9">
-        <v>768728707.533</v>
+        <v>788023876.936</v>
       </c>
       <c r="I9">
-        <v>273328617.455</v>
+        <v>312236114.3279999</v>
       </c>
       <c r="J9">
-        <v>1298118361.648</v>
+        <v>1289712369.578</v>
       </c>
       <c r="K9">
-        <v>164273304433.123</v>
+        <v>30782237914.626</v>
       </c>
       <c r="L9">
-        <v>105774371016.66</v>
+        <v>18880034051.958</v>
       </c>
       <c r="M9">
-        <v>231614962791.515</v>
+        <v>44296814147.034</v>
       </c>
     </row>
     <row r="10">
@@ -772,40 +772,40 @@
         </is>
       </c>
       <c r="B10">
-        <v>242659.842</v>
+        <v>243069.369</v>
       </c>
       <c r="C10">
-        <v>152339.202</v>
+        <v>153163.119</v>
       </c>
       <c r="D10">
-        <v>345739.198</v>
+        <v>345559.547</v>
       </c>
       <c r="E10">
-        <v>1575536.781</v>
+        <v>574082.25</v>
       </c>
       <c r="F10">
-        <v>1031993.788</v>
+        <v>379122.522</v>
       </c>
       <c r="G10">
-        <v>2206178.232</v>
+        <v>793760.014</v>
       </c>
       <c r="H10">
-        <v>768728707.533</v>
+        <v>788023876.936</v>
       </c>
       <c r="I10">
-        <v>273328617.455</v>
+        <v>312236114.3279999</v>
       </c>
       <c r="J10">
-        <v>1298118361.648</v>
+        <v>1289712369.578</v>
       </c>
       <c r="K10">
-        <v>209897444933.083</v>
+        <v>76406378414.586</v>
       </c>
       <c r="L10">
-        <v>137368078864.935</v>
+        <v>50473741900.233</v>
       </c>
       <c r="M10">
-        <v>292755124070.968</v>
+        <v>105436975426.487</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_disease.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease.xlsx
@@ -1,21 +1,98 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/steps/output/Tables/2019/Resampling/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9FE1AC-E0C3-B74F-83E5-E30B2752C363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="8980" yWindow="1620" windowWidth="10000" windowHeight="9680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_sup</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_sup</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_sup</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_sup</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>bc</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +140,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +192,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +226,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +261,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,88 +437,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_sup</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_sup</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_sup</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_sup</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <v>37422.697</v>
       </c>
       <c r="C2">
-        <v>26218.378</v>
+        <v>26218.378000000001</v>
       </c>
       <c r="D2">
         <v>49806.12</v>
@@ -440,10 +511,10 @@
         <v>343092.978</v>
       </c>
       <c r="F2">
-        <v>237289.928</v>
+        <v>237289.92800000001</v>
       </c>
       <c r="G2">
-        <v>459909.306</v>
+        <v>459909.30599999998</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,63 +526,59 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>45624140499.96</v>
+        <v>45624140499.959999</v>
       </c>
       <c r="L2">
-        <v>31593707848.275</v>
+        <v>31593707848.275002</v>
       </c>
       <c r="M2">
-        <v>61140161279.453</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+        <v>61140161279.453003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <v>10362.885</v>
       </c>
       <c r="C3">
-        <v>6020.804</v>
+        <v>6020.8040000000001</v>
       </c>
       <c r="D3">
-        <v>15495.914</v>
+        <v>15495.914000000001</v>
       </c>
       <c r="E3">
-        <v>7346.729</v>
+        <v>7346.7290000000003</v>
       </c>
       <c r="F3">
-        <v>4259.595</v>
+        <v>4259.5950000000003</v>
       </c>
       <c r="G3">
-        <v>11004.646</v>
+        <v>11004.646000000001</v>
       </c>
       <c r="H3">
-        <v>217120144.99</v>
+        <v>217120144.99000001</v>
       </c>
       <c r="I3">
         <v>125909963.324</v>
       </c>
       <c r="J3">
-        <v>324924454.115</v>
+        <v>324924454.11500001</v>
       </c>
       <c r="K3">
-        <v>977428520.8940001</v>
+        <v>977428520.89400005</v>
       </c>
       <c r="L3">
-        <v>567723926.901</v>
+        <v>567723926.90100002</v>
       </c>
       <c r="M3">
-        <v>1462932249.94</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
+        <v>1462932249.9400001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
         <v>3974.078</v>
@@ -520,41 +587,39 @@
         <v>2842.134</v>
       </c>
       <c r="D4">
-        <v>5104.737</v>
+        <v>5104.7370000000001</v>
       </c>
       <c r="E4">
-        <v>6273.717</v>
+        <v>6273.7169999999996</v>
       </c>
       <c r="F4">
-        <v>4459.626</v>
+        <v>4459.6260000000002</v>
       </c>
       <c r="G4">
-        <v>8094.704</v>
+        <v>8094.7039999999997</v>
       </c>
       <c r="H4">
-        <v>186793574.592</v>
+        <v>186793574.59200001</v>
       </c>
       <c r="I4">
         <v>133630235.149</v>
       </c>
       <c r="J4">
-        <v>240231003.475</v>
+        <v>240231003.47499999</v>
       </c>
       <c r="K4">
-        <v>834371355.705</v>
+        <v>834371355.70500004</v>
       </c>
       <c r="L4">
-        <v>593160156.525</v>
+        <v>593160156.52499998</v>
       </c>
       <c r="M4">
-        <v>1074735879.446</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
+        <v>1074735879.4460001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>4822.37</v>
@@ -563,28 +628,28 @@
         <v>86.91</v>
       </c>
       <c r="D5">
-        <v>10164.478</v>
+        <v>10164.477999999999</v>
       </c>
       <c r="E5">
-        <v>4711.708</v>
+        <v>4711.7079999999996</v>
       </c>
       <c r="F5">
-        <v>80.953</v>
+        <v>80.953000000000003</v>
       </c>
       <c r="G5">
-        <v>9955.523999999999</v>
+        <v>9955.5239999999994</v>
       </c>
       <c r="H5">
-        <v>71472523.529</v>
+        <v>71472523.528999999</v>
       </c>
       <c r="I5">
         <v>1297064.639</v>
       </c>
       <c r="J5">
-        <v>150575407.547</v>
+        <v>150575407.54699999</v>
       </c>
       <c r="K5">
-        <v>626513628.053</v>
+        <v>626513628.05299997</v>
       </c>
       <c r="L5">
         <v>10732275.533</v>
@@ -593,11 +658,9 @@
         <v>1324485775.98</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
         <v>6369.549</v>
@@ -609,7 +672,7 @@
         <v>12591.492</v>
       </c>
       <c r="E6">
-        <v>8778.665000000001</v>
+        <v>8778.6650000000009</v>
       </c>
       <c r="F6">
         <v>-1.089</v>
@@ -624,75 +687,71 @@
         <v>50346.98</v>
       </c>
       <c r="J6">
-        <v>459470588.237</v>
+        <v>459470588.23699999</v>
       </c>
       <c r="K6">
         <v>1169215292.244</v>
       </c>
       <c r="L6">
-        <v>2011404.592</v>
+        <v>2011404.5919999999</v>
       </c>
       <c r="M6">
         <v>2319917400.743</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
         <v>3527.373</v>
       </c>
       <c r="C7">
-        <v>2260.885</v>
+        <v>2260.8850000000002</v>
       </c>
       <c r="D7">
-        <v>5035.171</v>
+        <v>5035.1710000000003</v>
       </c>
       <c r="E7">
-        <v>3459.804</v>
+        <v>3459.8040000000001</v>
       </c>
       <c r="F7">
-        <v>2204.737</v>
+        <v>2204.7370000000001</v>
       </c>
       <c r="G7">
-        <v>4933.533</v>
+        <v>4933.5330000000004</v>
       </c>
       <c r="H7">
         <v>80344085.684</v>
       </c>
       <c r="I7">
-        <v>51348504.236</v>
+        <v>51348504.236000001</v>
       </c>
       <c r="J7">
         <v>114510916.204</v>
       </c>
       <c r="K7">
-        <v>459403645.738</v>
+        <v>459403645.73799998</v>
       </c>
       <c r="L7">
-        <v>293979741.437</v>
+        <v>293979741.43699998</v>
       </c>
       <c r="M7">
-        <v>658128229.543</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+        <v>658128229.54299998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>176590.417</v>
+        <v>176590.41699999999</v>
       </c>
       <c r="C8">
         <v>115735.145</v>
       </c>
       <c r="D8">
-        <v>247361.635</v>
+        <v>247361.63500000001</v>
       </c>
       <c r="E8">
         <v>200418.649</v>
@@ -701,7 +760,7 @@
         <v>130828.772</v>
       </c>
       <c r="G8">
-        <v>282432.251</v>
+        <v>282432.25099999999</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -713,72 +772,68 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>26715305471.992</v>
+        <v>26715305471.992001</v>
       </c>
       <c r="L8">
-        <v>17412426546.97</v>
+        <v>17412426546.970001</v>
       </c>
       <c r="M8">
-        <v>37456614611.382</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
+        <v>37456614611.382004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>205646.672</v>
+        <v>205646.67199999999</v>
       </c>
       <c r="C9">
-        <v>126944.741</v>
+        <v>126944.74099999999</v>
       </c>
       <c r="D9">
-        <v>295753.427</v>
+        <v>295753.42700000003</v>
       </c>
       <c r="E9">
         <v>230989.272</v>
       </c>
       <c r="F9">
-        <v>141832.594</v>
+        <v>141832.59400000001</v>
       </c>
       <c r="G9">
-        <v>333850.708</v>
+        <v>333850.70799999998</v>
       </c>
       <c r="H9">
-        <v>788023876.936</v>
+        <v>788023876.93599999</v>
       </c>
       <c r="I9">
-        <v>312236114.3279999</v>
+        <v>312236114.32799989</v>
       </c>
       <c r="J9">
-        <v>1289712369.578</v>
+        <v>1289712369.5780001</v>
       </c>
       <c r="K9">
-        <v>30782237914.626</v>
+        <v>30782237914.625999</v>
       </c>
       <c r="L9">
         <v>18880034051.958</v>
       </c>
       <c r="M9">
-        <v>44296814147.034</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>44296814147.033997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
       <c r="B10">
-        <v>243069.369</v>
+        <v>243069.36900000001</v>
       </c>
       <c r="C10">
-        <v>153163.119</v>
+        <v>153163.11900000001</v>
       </c>
       <c r="D10">
-        <v>345559.547</v>
+        <v>345559.54700000002</v>
       </c>
       <c r="E10">
         <v>574082.25</v>
@@ -787,22 +842,22 @@
         <v>379122.522</v>
       </c>
       <c r="G10">
-        <v>793760.014</v>
+        <v>793760.01399999997</v>
       </c>
       <c r="H10">
-        <v>788023876.936</v>
+        <v>788023876.93599999</v>
       </c>
       <c r="I10">
-        <v>312236114.3279999</v>
+        <v>312236114.32799989</v>
       </c>
       <c r="J10">
-        <v>1289712369.578</v>
+        <v>1289712369.5780001</v>
       </c>
       <c r="K10">
-        <v>76406378414.586</v>
+        <v>76406378414.585999</v>
       </c>
       <c r="L10">
-        <v>50473741900.233</v>
+        <v>50473741900.233002</v>
       </c>
       <c r="M10">
         <v>105436975426.487</v>

--- a/output/Tables/2019/Resampling/HIA_per_disease.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease.xlsx
@@ -1,98 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/steps/output/Tables/2019/Resampling/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9FE1AC-E0C3-B74F-83E5-E30B2752C363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8980" yWindow="1620" windowWidth="10000" windowHeight="9680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_sup</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_sup</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_sup</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_sup</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>bc</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -192,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -226,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -261,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -437,84 +350,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_sup</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_sup</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_sup</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_sup</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
       </c>
       <c r="B2">
         <v>37422.697</v>
       </c>
       <c r="C2">
-        <v>26218.378000000001</v>
+        <v>26218.378</v>
       </c>
       <c r="D2">
         <v>49806.12</v>
       </c>
       <c r="E2">
-        <v>343092.978</v>
+        <v>57182.163</v>
       </c>
       <c r="F2">
-        <v>237289.92800000001</v>
+        <v>39548.321</v>
       </c>
       <c r="G2">
-        <v>459909.30599999998</v>
+        <v>76651.55100000001</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -526,241 +455,253 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>45624140499.959999</v>
+        <v>7604023416.66</v>
       </c>
       <c r="L2">
-        <v>31593707848.275002</v>
+        <v>5265617974.712</v>
       </c>
       <c r="M2">
-        <v>61140161279.453003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
+        <v>10190026879.909</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
       </c>
       <c r="B3">
         <v>10362.885</v>
       </c>
       <c r="C3">
-        <v>6020.8040000000001</v>
+        <v>6020.804</v>
       </c>
       <c r="D3">
-        <v>15495.914000000001</v>
+        <v>15495.914</v>
       </c>
       <c r="E3">
-        <v>7346.7290000000003</v>
+        <v>1512.803</v>
       </c>
       <c r="F3">
-        <v>4259.5950000000003</v>
+        <v>876.359</v>
       </c>
       <c r="G3">
-        <v>11004.646000000001</v>
+        <v>2265.096</v>
       </c>
       <c r="H3">
-        <v>217120144.99000001</v>
+        <v>577611343.788</v>
       </c>
       <c r="I3">
-        <v>125909963.324</v>
+        <v>334962115.632</v>
       </c>
       <c r="J3">
-        <v>324924454.11500001</v>
+        <v>864406435.337</v>
       </c>
       <c r="K3">
-        <v>977428520.89400005</v>
+        <v>201235127.08</v>
       </c>
       <c r="L3">
-        <v>567723926.90100002</v>
+        <v>116807038.279</v>
       </c>
       <c r="M3">
-        <v>1462932249.9400001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
+        <v>301340237.54</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
       </c>
       <c r="B4">
-        <v>3974.078</v>
+        <v>767.569</v>
       </c>
       <c r="C4">
-        <v>2842.134</v>
+        <v>14.536</v>
       </c>
       <c r="D4">
-        <v>5104.7370000000001</v>
+        <v>1628.987</v>
       </c>
       <c r="E4">
-        <v>6273.7169999999996</v>
+        <v>205.669</v>
       </c>
       <c r="F4">
-        <v>4459.6260000000002</v>
+        <v>3.757</v>
       </c>
       <c r="G4">
-        <v>8094.7039999999997</v>
+        <v>438.429</v>
       </c>
       <c r="H4">
-        <v>186793574.59200001</v>
+        <v>33816727.337</v>
       </c>
       <c r="I4">
-        <v>133630235.149</v>
+        <v>651945.099</v>
       </c>
       <c r="J4">
-        <v>240231003.47499999</v>
+        <v>71788284.93799999</v>
       </c>
       <c r="K4">
-        <v>834371355.70500004</v>
+        <v>27359002.271</v>
       </c>
       <c r="L4">
-        <v>593160156.52499998</v>
+        <v>497463.808</v>
       </c>
       <c r="M4">
-        <v>1074735879.4460001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
+        <v>58120463.11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
       </c>
       <c r="B5">
-        <v>4822.37</v>
+        <v>4827.073</v>
       </c>
       <c r="C5">
-        <v>86.91</v>
+        <v>86.61</v>
       </c>
       <c r="D5">
-        <v>10164.477999999999</v>
+        <v>10166.022</v>
       </c>
       <c r="E5">
-        <v>4711.7079999999996</v>
+        <v>785.417</v>
       </c>
       <c r="F5">
-        <v>80.953000000000003</v>
+        <v>13.406</v>
       </c>
       <c r="G5">
-        <v>9955.5239999999994</v>
+        <v>1657.574</v>
       </c>
       <c r="H5">
-        <v>71472523.528999999</v>
+        <v>71390092.395</v>
       </c>
       <c r="I5">
-        <v>1297064.639</v>
+        <v>1285798.723</v>
       </c>
       <c r="J5">
-        <v>150575407.54699999</v>
+        <v>150411916.51</v>
       </c>
       <c r="K5">
-        <v>626513628.05299997</v>
+        <v>104439149.344</v>
       </c>
       <c r="L5">
-        <v>10732275.533</v>
+        <v>1768711.701</v>
       </c>
       <c r="M5">
-        <v>1324485775.98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
+        <v>221280517.595</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
       </c>
       <c r="B6">
-        <v>6369.549</v>
+        <v>6373.388</v>
       </c>
       <c r="C6">
-        <v>-1.137</v>
+        <v>3.8</v>
       </c>
       <c r="D6">
-        <v>12591.492</v>
+        <v>12612.986</v>
       </c>
       <c r="E6">
-        <v>8778.6650000000009</v>
+        <v>1482.854</v>
       </c>
       <c r="F6">
-        <v>-1.089</v>
+        <v>-0.03</v>
       </c>
       <c r="G6">
-        <v>17430.05</v>
+        <v>2950.92</v>
       </c>
       <c r="H6">
-        <v>232293548.141</v>
+        <v>478416173.622</v>
       </c>
       <c r="I6">
-        <v>50346.98</v>
+        <v>201055.448</v>
       </c>
       <c r="J6">
-        <v>459470588.23699999</v>
+        <v>945010448.528</v>
       </c>
       <c r="K6">
-        <v>1169215292.244</v>
+        <v>197532797.944</v>
       </c>
       <c r="L6">
-        <v>2011404.5919999999</v>
+        <v>98747.716</v>
       </c>
       <c r="M6">
-        <v>2319917400.743</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
+        <v>392258706.354</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
       </c>
       <c r="B7">
-        <v>3527.373</v>
+        <v>3531.143</v>
       </c>
       <c r="C7">
-        <v>2260.8850000000002</v>
+        <v>2253.645</v>
       </c>
       <c r="D7">
-        <v>5035.1710000000003</v>
+        <v>5036.468</v>
       </c>
       <c r="E7">
-        <v>3459.8040000000001</v>
+        <v>785.807</v>
       </c>
       <c r="F7">
-        <v>2204.7370000000001</v>
+        <v>501.962</v>
       </c>
       <c r="G7">
-        <v>4933.5330000000004</v>
+        <v>1121.332</v>
       </c>
       <c r="H7">
-        <v>80344085.684</v>
+        <v>59420701.757</v>
       </c>
       <c r="I7">
-        <v>51348504.236000001</v>
+        <v>37933832.017</v>
       </c>
       <c r="J7">
-        <v>114510916.204</v>
+        <v>84891561.303</v>
       </c>
       <c r="K7">
-        <v>459403645.73799998</v>
+        <v>104574568.623</v>
       </c>
       <c r="L7">
-        <v>293979741.43699998</v>
+        <v>66742889.502</v>
       </c>
       <c r="M7">
-        <v>658128229.54299998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
+        <v>149357377.433</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
       </c>
       <c r="B8">
-        <v>176590.41699999999</v>
+        <v>176535.635</v>
       </c>
       <c r="C8">
-        <v>115735.145</v>
+        <v>115856.311</v>
       </c>
       <c r="D8">
-        <v>247361.63500000001</v>
+        <v>247087.924</v>
       </c>
       <c r="E8">
-        <v>200418.649</v>
+        <v>200587.207</v>
       </c>
       <c r="F8">
-        <v>130828.772</v>
+        <v>131032.158</v>
       </c>
       <c r="G8">
-        <v>282432.25099999999</v>
+        <v>282459.326</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -772,95 +713,99 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>26715305471.992001</v>
+        <v>26724254724.541</v>
       </c>
       <c r="L8">
-        <v>17412426546.970001</v>
+        <v>17477290573.503</v>
       </c>
       <c r="M8">
-        <v>37456614611.382004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>20</v>
+        <v>37522846067.981</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Morbidity</t>
+        </is>
       </c>
       <c r="B9">
-        <v>205646.67199999999</v>
+        <v>202397.693</v>
       </c>
       <c r="C9">
-        <v>126944.74099999999</v>
+        <v>124235.706</v>
       </c>
       <c r="D9">
-        <v>295753.42700000003</v>
+        <v>292028.301</v>
       </c>
       <c r="E9">
-        <v>230989.272</v>
+        <v>205359.757</v>
       </c>
       <c r="F9">
-        <v>141832.59400000001</v>
+        <v>132427.612</v>
       </c>
       <c r="G9">
-        <v>333850.70799999998</v>
+        <v>290892.677</v>
       </c>
       <c r="H9">
-        <v>788023876.93599999</v>
+        <v>1220655038.899</v>
       </c>
       <c r="I9">
-        <v>312236114.32799989</v>
+        <v>375034746.919</v>
       </c>
       <c r="J9">
-        <v>1289712369.5780001</v>
+        <v>2116508646.616</v>
       </c>
       <c r="K9">
-        <v>30782237914.625999</v>
+        <v>27359395369.803</v>
       </c>
       <c r="L9">
-        <v>18880034051.958</v>
+        <v>17663205424.509</v>
       </c>
       <c r="M9">
-        <v>44296814147.033997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>21</v>
+        <v>38645203370.013</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="B10">
-        <v>243069.36900000001</v>
+        <v>239820.39</v>
       </c>
       <c r="C10">
-        <v>153163.11900000001</v>
+        <v>150454.084</v>
       </c>
       <c r="D10">
-        <v>345559.54700000002</v>
+        <v>341834.421</v>
       </c>
       <c r="E10">
-        <v>574082.25</v>
+        <v>262541.92</v>
       </c>
       <c r="F10">
-        <v>379122.522</v>
+        <v>171975.933</v>
       </c>
       <c r="G10">
-        <v>793760.01399999997</v>
+        <v>367544.228</v>
       </c>
       <c r="H10">
-        <v>788023876.93599999</v>
+        <v>1220655038.899</v>
       </c>
       <c r="I10">
-        <v>312236114.32799989</v>
+        <v>375034746.919</v>
       </c>
       <c r="J10">
-        <v>1289712369.5780001</v>
+        <v>2116508646.616</v>
       </c>
       <c r="K10">
-        <v>76406378414.585999</v>
+        <v>34963418786.463</v>
       </c>
       <c r="L10">
-        <v>50473741900.233002</v>
+        <v>22928823399.221</v>
       </c>
       <c r="M10">
-        <v>105436975426.487</v>
+        <v>48835230249.922</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_disease.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>37422.697</v>
+        <v>58557.991</v>
       </c>
       <c r="C2">
-        <v>26218.378</v>
+        <v>49945.82</v>
       </c>
       <c r="D2">
-        <v>49806.12</v>
+        <v>66993.103</v>
       </c>
       <c r="E2">
-        <v>57182.163</v>
+        <v>101034.279</v>
       </c>
       <c r="F2">
-        <v>39548.321</v>
+        <v>86546.47900000001</v>
       </c>
       <c r="G2">
-        <v>76651.55100000001</v>
+        <v>114715.82</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>7604023416.66</v>
+        <v>13436200483.628</v>
       </c>
       <c r="L2">
-        <v>5265617974.712</v>
+        <v>11513856177.037</v>
       </c>
       <c r="M2">
-        <v>10190026879.909</v>
+        <v>15257567291.504</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>10362.885</v>
+        <v>39415.958</v>
       </c>
       <c r="C3">
-        <v>6020.804</v>
+        <v>24947.584</v>
       </c>
       <c r="D3">
-        <v>15495.914</v>
+        <v>53141.374</v>
       </c>
       <c r="E3">
-        <v>1512.803</v>
+        <v>5727.182</v>
       </c>
       <c r="F3">
-        <v>876.359</v>
+        <v>3629.11</v>
       </c>
       <c r="G3">
-        <v>2265.096</v>
+        <v>7706.852</v>
       </c>
       <c r="H3">
-        <v>577611343.788</v>
+        <v>2196270736.583</v>
       </c>
       <c r="I3">
-        <v>334962115.632</v>
+        <v>1389946392.788</v>
       </c>
       <c r="J3">
-        <v>864406435.337</v>
+        <v>2959480475.341</v>
       </c>
       <c r="K3">
-        <v>201235127.08</v>
+        <v>761844866.878</v>
       </c>
       <c r="L3">
-        <v>116807038.279</v>
+        <v>481826982.528</v>
       </c>
       <c r="M3">
-        <v>301340237.54</v>
+        <v>1025348946.677</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>767.569</v>
+        <v>1258.357</v>
       </c>
       <c r="C4">
-        <v>14.536</v>
+        <v>31.988</v>
       </c>
       <c r="D4">
-        <v>1628.987</v>
+        <v>2465.964</v>
       </c>
       <c r="E4">
-        <v>205.669</v>
+        <v>350.837</v>
       </c>
       <c r="F4">
-        <v>3.757</v>
+        <v>8.646000000000001</v>
       </c>
       <c r="G4">
-        <v>438.429</v>
+        <v>687.718</v>
       </c>
       <c r="H4">
-        <v>33816727.337</v>
+        <v>55479244.971</v>
       </c>
       <c r="I4">
-        <v>651945.099</v>
+        <v>1408763.842</v>
       </c>
       <c r="J4">
-        <v>71788284.93799999</v>
+        <v>108609624.73</v>
       </c>
       <c r="K4">
-        <v>27359002.271</v>
+        <v>46667542.033</v>
       </c>
       <c r="L4">
-        <v>497463.808</v>
+        <v>1149942.194</v>
       </c>
       <c r="M4">
-        <v>58120463.11</v>
+        <v>91338353.043</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>4827.073</v>
+        <v>30771.841</v>
       </c>
       <c r="C5">
-        <v>86.61</v>
+        <v>770.663</v>
       </c>
       <c r="D5">
-        <v>10166.022</v>
+        <v>60274.446</v>
       </c>
       <c r="E5">
-        <v>785.417</v>
+        <v>7659.029</v>
       </c>
       <c r="F5">
-        <v>13.406</v>
+        <v>194.308</v>
       </c>
       <c r="G5">
-        <v>1657.574</v>
+        <v>15003.61</v>
       </c>
       <c r="H5">
-        <v>71390092.395</v>
+        <v>455720026.337</v>
       </c>
       <c r="I5">
-        <v>1285798.723</v>
+        <v>11469607.304</v>
       </c>
       <c r="J5">
-        <v>150411916.51</v>
+        <v>891777840.605</v>
       </c>
       <c r="K5">
-        <v>104439149.344</v>
+        <v>1017869665.832</v>
       </c>
       <c r="L5">
-        <v>1768711.701</v>
+        <v>25603646.386</v>
       </c>
       <c r="M5">
-        <v>221280517.595</v>
+        <v>1993877475.893</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>6373.388</v>
+        <v>6503.687</v>
       </c>
       <c r="C6">
-        <v>3.8</v>
+        <v>8.622</v>
       </c>
       <c r="D6">
-        <v>12612.986</v>
+        <v>12143.443</v>
       </c>
       <c r="E6">
-        <v>1482.854</v>
+        <v>2109.445</v>
       </c>
       <c r="F6">
-        <v>-0.03</v>
+        <v>2.698</v>
       </c>
       <c r="G6">
-        <v>2950.92</v>
+        <v>3944.985</v>
       </c>
       <c r="H6">
-        <v>478416173.622</v>
+        <v>488757146.831</v>
       </c>
       <c r="I6">
-        <v>201055.448</v>
+        <v>592350.6850000001</v>
       </c>
       <c r="J6">
-        <v>945010448.528</v>
+        <v>913408209.035</v>
       </c>
       <c r="K6">
-        <v>197532797.944</v>
+        <v>280587639.026</v>
       </c>
       <c r="L6">
-        <v>98747.716</v>
+        <v>459873.942</v>
       </c>
       <c r="M6">
-        <v>392258706.354</v>
+        <v>524835213.408</v>
       </c>
     </row>
     <row r="7">
@@ -643,40 +643,40 @@
         </is>
       </c>
       <c r="B7">
-        <v>3531.143</v>
+        <v>13422.471</v>
       </c>
       <c r="C7">
-        <v>2253.645</v>
+        <v>9811.249</v>
       </c>
       <c r="D7">
-        <v>5036.468</v>
+        <v>16881.992</v>
       </c>
       <c r="E7">
-        <v>785.807</v>
+        <v>3438.387</v>
       </c>
       <c r="F7">
-        <v>501.962</v>
+        <v>2521.748</v>
       </c>
       <c r="G7">
-        <v>1121.332</v>
+        <v>4303.11</v>
       </c>
       <c r="H7">
-        <v>59420701.757</v>
+        <v>226030128.455</v>
       </c>
       <c r="I7">
-        <v>37933832.017</v>
+        <v>165050084.44</v>
       </c>
       <c r="J7">
-        <v>84891561.303</v>
+        <v>284369554.96</v>
       </c>
       <c r="K7">
-        <v>104574568.623</v>
+        <v>457365624.97</v>
       </c>
       <c r="L7">
-        <v>66742889.502</v>
+        <v>335119870.505</v>
       </c>
       <c r="M7">
-        <v>149357377.433</v>
+        <v>572477073.228</v>
       </c>
     </row>
     <row r="8">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>176535.635</v>
+        <v>151751.087</v>
       </c>
       <c r="C8">
-        <v>115856.311</v>
+        <v>113659.409</v>
       </c>
       <c r="D8">
-        <v>247087.924</v>
+        <v>187054.892</v>
       </c>
       <c r="E8">
-        <v>200587.207</v>
+        <v>148488.137</v>
       </c>
       <c r="F8">
-        <v>131032.158</v>
+        <v>110847.372</v>
       </c>
       <c r="G8">
-        <v>282459.326</v>
+        <v>183380.128</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>26724254724.541</v>
+        <v>19747986835.863</v>
       </c>
       <c r="L8">
-        <v>17477290573.503</v>
+        <v>14745485651.581</v>
       </c>
       <c r="M8">
-        <v>37522846067.981</v>
+        <v>24408111325.769</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>202397.693</v>
+        <v>243123.401</v>
       </c>
       <c r="C9">
-        <v>124235.706</v>
+        <v>149229.515</v>
       </c>
       <c r="D9">
-        <v>292028.301</v>
+        <v>331962.111</v>
       </c>
       <c r="E9">
-        <v>205359.757</v>
+        <v>167773.017</v>
       </c>
       <c r="F9">
-        <v>132427.612</v>
+        <v>117203.882</v>
       </c>
       <c r="G9">
-        <v>290892.677</v>
+        <v>215026.403</v>
       </c>
       <c r="H9">
-        <v>1220655038.899</v>
+        <v>3422257283.177</v>
       </c>
       <c r="I9">
-        <v>375034746.919</v>
+        <v>1568467199.059</v>
       </c>
       <c r="J9">
-        <v>2116508646.616</v>
+        <v>5157645704.671</v>
       </c>
       <c r="K9">
-        <v>27359395369.803</v>
+        <v>22312322174.602</v>
       </c>
       <c r="L9">
-        <v>17663205424.509</v>
+        <v>15589645967.136</v>
       </c>
       <c r="M9">
-        <v>38645203370.013</v>
+        <v>28615988388.018</v>
       </c>
     </row>
     <row r="10">
@@ -772,40 +772,40 @@
         </is>
       </c>
       <c r="B10">
-        <v>239820.39</v>
+        <v>301681.392</v>
       </c>
       <c r="C10">
-        <v>150454.084</v>
+        <v>199175.335</v>
       </c>
       <c r="D10">
-        <v>341834.421</v>
+        <v>398955.214</v>
       </c>
       <c r="E10">
-        <v>262541.92</v>
+        <v>268807.296</v>
       </c>
       <c r="F10">
-        <v>171975.933</v>
+        <v>203750.361</v>
       </c>
       <c r="G10">
-        <v>367544.228</v>
+        <v>329742.223</v>
       </c>
       <c r="H10">
-        <v>1220655038.899</v>
+        <v>3422257283.177</v>
       </c>
       <c r="I10">
-        <v>375034746.919</v>
+        <v>1568467199.059</v>
       </c>
       <c r="J10">
-        <v>2116508646.616</v>
+        <v>5157645704.671</v>
       </c>
       <c r="K10">
-        <v>34963418786.463</v>
+        <v>35748522658.23</v>
       </c>
       <c r="L10">
-        <v>22928823399.221</v>
+        <v>27103502144.173</v>
       </c>
       <c r="M10">
-        <v>48835230249.922</v>
+        <v>43873555679.522</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_disease.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease.xlsx
@@ -1,21 +1,110 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/Resampling/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A054DDA9-38DD-3740-BF3D-8F0D01FFEE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="32840" yWindow="-1260" windowWidth="29240" windowHeight="15140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_sup</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_sup</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_sup</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_sup</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>bc</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +152,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +204,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +238,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +273,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,97 +449,81 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_sup</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_sup</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_sup</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_sup</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>58557.991</v>
+        <v>58557.991000000002</v>
       </c>
       <c r="C2">
         <v>49945.82</v>
       </c>
       <c r="D2">
-        <v>66993.103</v>
+        <v>66993.103000000003</v>
       </c>
       <c r="E2">
-        <v>101034.279</v>
+        <v>101034.27899999999</v>
       </c>
       <c r="F2">
-        <v>86546.47900000001</v>
+        <v>86546.479000000007</v>
       </c>
       <c r="G2">
         <v>114715.82</v>
@@ -458,47 +541,45 @@
         <v>13436200483.628</v>
       </c>
       <c r="L2">
-        <v>11513856177.037</v>
+        <v>11513856177.037001</v>
       </c>
       <c r="M2">
         <v>15257567291.504</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>39415.958</v>
+        <v>39415.957999999999</v>
       </c>
       <c r="C3">
-        <v>24947.584</v>
+        <v>24947.583999999999</v>
       </c>
       <c r="D3">
-        <v>53141.374</v>
+        <v>53141.374000000003</v>
       </c>
       <c r="E3">
-        <v>5727.182</v>
+        <v>5727.1819999999998</v>
       </c>
       <c r="F3">
         <v>3629.11</v>
       </c>
       <c r="G3">
-        <v>7706.852</v>
+        <v>7706.8519999999999</v>
       </c>
       <c r="H3">
-        <v>2196270736.583</v>
+        <v>2196270736.5830002</v>
       </c>
       <c r="I3">
-        <v>1389946392.788</v>
+        <v>1389946392.7880001</v>
       </c>
       <c r="J3">
-        <v>2959480475.341</v>
+        <v>2959480475.3410001</v>
       </c>
       <c r="K3">
-        <v>761844866.878</v>
+        <v>761844866.87800002</v>
       </c>
       <c r="L3">
         <v>481826982.528</v>
@@ -507,11 +588,9 @@
         <v>1025348946.677</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
         <v>1258.357</v>
@@ -520,22 +599,22 @@
         <v>31.988</v>
       </c>
       <c r="D4">
-        <v>2465.964</v>
+        <v>2465.9639999999999</v>
       </c>
       <c r="E4">
-        <v>350.837</v>
+        <v>350.83699999999999</v>
       </c>
       <c r="F4">
-        <v>8.646000000000001</v>
+        <v>8.6460000000000008</v>
       </c>
       <c r="G4">
-        <v>687.718</v>
+        <v>687.71799999999996</v>
       </c>
       <c r="H4">
-        <v>55479244.971</v>
+        <v>55479244.971000001</v>
       </c>
       <c r="I4">
-        <v>1408763.842</v>
+        <v>1408763.8419999999</v>
       </c>
       <c r="J4">
         <v>108609624.73</v>
@@ -544,44 +623,42 @@
         <v>46667542.033</v>
       </c>
       <c r="L4">
-        <v>1149942.194</v>
+        <v>1149942.1939999999</v>
       </c>
       <c r="M4">
-        <v>91338353.043</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
+        <v>91338353.042999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>30771.841</v>
       </c>
       <c r="C5">
-        <v>770.663</v>
+        <v>770.66300000000001</v>
       </c>
       <c r="D5">
-        <v>60274.446</v>
+        <v>60274.446000000004</v>
       </c>
       <c r="E5">
-        <v>7659.029</v>
+        <v>7659.0290000000005</v>
       </c>
       <c r="F5">
-        <v>194.308</v>
+        <v>194.30799999999999</v>
       </c>
       <c r="G5">
         <v>15003.61</v>
       </c>
       <c r="H5">
-        <v>455720026.337</v>
+        <v>455720026.33700001</v>
       </c>
       <c r="I5">
         <v>11469607.304</v>
       </c>
       <c r="J5">
-        <v>891777840.605</v>
+        <v>891777840.60500002</v>
       </c>
       <c r="K5">
         <v>1017869665.832</v>
@@ -590,100 +667,94 @@
         <v>25603646.386</v>
       </c>
       <c r="M5">
-        <v>1993877475.893</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+        <v>1993877475.8929999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>6503.687</v>
+        <v>6503.6869999999999</v>
       </c>
       <c r="C6">
-        <v>8.622</v>
+        <v>8.6219999999999999</v>
       </c>
       <c r="D6">
-        <v>12143.443</v>
+        <v>12143.442999999999</v>
       </c>
       <c r="E6">
-        <v>2109.445</v>
+        <v>2109.4450000000002</v>
       </c>
       <c r="F6">
         <v>2.698</v>
       </c>
       <c r="G6">
-        <v>3944.985</v>
+        <v>3944.9850000000001</v>
       </c>
       <c r="H6">
-        <v>488757146.831</v>
+        <v>488757146.83099997</v>
       </c>
       <c r="I6">
-        <v>592350.6850000001</v>
+        <v>592350.68500000006</v>
       </c>
       <c r="J6">
-        <v>913408209.035</v>
+        <v>913408209.03499997</v>
       </c>
       <c r="K6">
-        <v>280587639.026</v>
+        <v>280587639.02600002</v>
       </c>
       <c r="L6">
-        <v>459873.942</v>
+        <v>459873.94199999998</v>
       </c>
       <c r="M6">
-        <v>524835213.408</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+        <v>524835213.40799999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
         <v>13422.471</v>
       </c>
       <c r="C7">
-        <v>9811.249</v>
+        <v>9811.2489999999998</v>
       </c>
       <c r="D7">
-        <v>16881.992</v>
+        <v>16881.991999999998</v>
       </c>
       <c r="E7">
-        <v>3438.387</v>
+        <v>3438.3870000000002</v>
       </c>
       <c r="F7">
         <v>2521.748</v>
       </c>
       <c r="G7">
-        <v>4303.11</v>
+        <v>4303.1099999999997</v>
       </c>
       <c r="H7">
-        <v>226030128.455</v>
+        <v>226030128.45500001</v>
       </c>
       <c r="I7">
         <v>165050084.44</v>
       </c>
       <c r="J7">
-        <v>284369554.96</v>
+        <v>284369554.95999998</v>
       </c>
       <c r="K7">
-        <v>457365624.97</v>
+        <v>457365624.97000003</v>
       </c>
       <c r="L7">
         <v>335119870.505</v>
       </c>
       <c r="M7">
-        <v>572477073.228</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+        <v>572477073.22800004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>151751.087</v>
@@ -692,10 +763,10 @@
         <v>113659.409</v>
       </c>
       <c r="D8">
-        <v>187054.892</v>
+        <v>187054.89199999999</v>
       </c>
       <c r="E8">
-        <v>148488.137</v>
+        <v>148488.13699999999</v>
       </c>
       <c r="F8">
         <v>110847.372</v>
@@ -713,38 +784,36 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>19747986835.863</v>
+        <v>19747986835.862999</v>
       </c>
       <c r="L8">
-        <v>14745485651.581</v>
+        <v>14745485651.580999</v>
       </c>
       <c r="M8">
-        <v>24408111325.769</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
+        <v>24408111325.769001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>243123.401</v>
+        <v>243123.40100000001</v>
       </c>
       <c r="C9">
-        <v>149229.515</v>
+        <v>149229.51500000001</v>
       </c>
       <c r="D9">
-        <v>331962.111</v>
+        <v>331962.11099999998</v>
       </c>
       <c r="E9">
-        <v>167773.017</v>
+        <v>167773.01699999999</v>
       </c>
       <c r="F9">
         <v>117203.882</v>
       </c>
       <c r="G9">
-        <v>215026.403</v>
+        <v>215026.40299999999</v>
       </c>
       <c r="H9">
         <v>3422257283.177</v>
@@ -753,35 +822,33 @@
         <v>1568467199.059</v>
       </c>
       <c r="J9">
-        <v>5157645704.671</v>
+        <v>5157645704.6709995</v>
       </c>
       <c r="K9">
-        <v>22312322174.602</v>
+        <v>22312322174.602001</v>
       </c>
       <c r="L9">
         <v>15589645967.136</v>
       </c>
       <c r="M9">
-        <v>28615988388.018</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>28615988388.018002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
       <c r="B10">
-        <v>301681.392</v>
+        <v>301681.39199999999</v>
       </c>
       <c r="C10">
-        <v>199175.335</v>
+        <v>199175.33499999999</v>
       </c>
       <c r="D10">
-        <v>398955.214</v>
+        <v>398955.21399999998</v>
       </c>
       <c r="E10">
-        <v>268807.296</v>
+        <v>268807.29599999997</v>
       </c>
       <c r="F10">
         <v>203750.361</v>
@@ -796,16 +863,16 @@
         <v>1568467199.059</v>
       </c>
       <c r="J10">
-        <v>5157645704.671</v>
+        <v>5157645704.6709995</v>
       </c>
       <c r="K10">
-        <v>35748522658.23</v>
+        <v>35748522658.230003</v>
       </c>
       <c r="L10">
         <v>27103502144.173</v>
       </c>
       <c r="M10">
-        <v>43873555679.522</v>
+        <v>43873555679.522003</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_disease.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease.xlsx
@@ -1,110 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/Resampling/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A054DDA9-38DD-3740-BF3D-8F0D01FFEE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32840" yWindow="-1260" windowWidth="29240" windowHeight="15140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_sup</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_sup</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_sup</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_sup</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>bc</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -204,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -238,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -273,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -449,84 +350,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_sup</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_sup</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_sup</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_sup</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
       </c>
       <c r="B2">
-        <v>58557.991000000002</v>
+        <v>58557.991</v>
       </c>
       <c r="C2">
         <v>49945.82</v>
       </c>
       <c r="D2">
-        <v>66993.103000000003</v>
+        <v>66993.103</v>
       </c>
       <c r="E2">
-        <v>101034.27899999999</v>
+        <v>606205.674</v>
       </c>
       <c r="F2">
-        <v>86546.479000000007</v>
+        <v>519278.874</v>
       </c>
       <c r="G2">
-        <v>114715.82</v>
+        <v>688294.921</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -538,341 +455,314 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>13436200483.628</v>
+        <v>80617202901.769</v>
       </c>
       <c r="L2">
-        <v>11513856177.037001</v>
+        <v>69083137062.224</v>
       </c>
       <c r="M2">
-        <v>15257567291.504</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
+        <v>91545403749.026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
       </c>
       <c r="B3">
-        <v>39415.957999999999</v>
+        <v>39415.958</v>
       </c>
       <c r="C3">
-        <v>24947.583999999999</v>
+        <v>24947.584</v>
       </c>
       <c r="D3">
-        <v>53141.374000000003</v>
+        <v>53141.374</v>
       </c>
       <c r="E3">
-        <v>5727.1819999999998</v>
+        <v>34353.596</v>
       </c>
       <c r="F3">
-        <v>3629.11</v>
+        <v>21789.613</v>
       </c>
       <c r="G3">
-        <v>7706.8519999999999</v>
+        <v>46209.354</v>
       </c>
       <c r="H3">
-        <v>2196270736.5830002</v>
+        <v>2196270736.583</v>
       </c>
       <c r="I3">
-        <v>1389946392.7880001</v>
+        <v>1389946392.788</v>
       </c>
       <c r="J3">
-        <v>2959480475.3410001</v>
+        <v>2959480475.341</v>
       </c>
       <c r="K3">
-        <v>761844866.87800002</v>
+        <v>4570009021.463</v>
       </c>
       <c r="L3">
-        <v>481826982.528</v>
+        <v>2893480693.145</v>
       </c>
       <c r="M3">
-        <v>1025348946.677</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
+        <v>6145854840.993</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
       </c>
       <c r="B4">
-        <v>1258.357</v>
+        <v>30761.584</v>
       </c>
       <c r="C4">
-        <v>31.988</v>
+        <v>782.3390000000001</v>
       </c>
       <c r="D4">
-        <v>2465.9639999999999</v>
+        <v>60291.062</v>
       </c>
       <c r="E4">
-        <v>350.83699999999999</v>
+        <v>45968.456</v>
       </c>
       <c r="F4">
-        <v>8.6460000000000008</v>
+        <v>1161.487</v>
       </c>
       <c r="G4">
-        <v>687.71799999999996</v>
+        <v>90086.645</v>
       </c>
       <c r="H4">
-        <v>55479244.971000001</v>
+        <v>455566760.471</v>
       </c>
       <c r="I4">
-        <v>1408763.8419999999</v>
+        <v>11529871.341</v>
       </c>
       <c r="J4">
-        <v>108609624.73</v>
+        <v>892262397.48</v>
       </c>
       <c r="K4">
-        <v>46667542.033</v>
+        <v>6113416255.102</v>
       </c>
       <c r="L4">
-        <v>1149942.1939999999</v>
+        <v>155325493.918</v>
       </c>
       <c r="M4">
-        <v>91338353.042999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
+        <v>11973389123.823</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
       </c>
       <c r="B5">
-        <v>30771.841</v>
+        <v>6500.221</v>
       </c>
       <c r="C5">
-        <v>770.66300000000001</v>
+        <v>7.931</v>
       </c>
       <c r="D5">
-        <v>60274.446000000004</v>
+        <v>12139.91</v>
       </c>
       <c r="E5">
-        <v>7659.0290000000005</v>
+        <v>12663.258</v>
       </c>
       <c r="F5">
-        <v>194.30799999999999</v>
+        <v>27.113</v>
       </c>
       <c r="G5">
-        <v>15003.61</v>
+        <v>23667.019</v>
       </c>
       <c r="H5">
-        <v>455720026.33700001</v>
+        <v>488959452.671</v>
       </c>
       <c r="I5">
-        <v>11469607.304</v>
+        <v>320739.813</v>
       </c>
       <c r="J5">
-        <v>891777840.60500002</v>
+        <v>913065716.702</v>
       </c>
       <c r="K5">
-        <v>1017869665.832</v>
+        <v>1684704108.369</v>
       </c>
       <c r="L5">
-        <v>25603646.386</v>
+        <v>1263674.048</v>
       </c>
       <c r="M5">
-        <v>1993877475.8929999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
+        <v>3148405920.294</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
       </c>
       <c r="B6">
-        <v>6503.6869999999999</v>
+        <v>13429.6</v>
       </c>
       <c r="C6">
-        <v>8.6219999999999999</v>
+        <v>9799.373</v>
       </c>
       <c r="D6">
-        <v>12143.442999999999</v>
+        <v>16893.385</v>
       </c>
       <c r="E6">
-        <v>2109.4450000000002</v>
+        <v>20636.268</v>
       </c>
       <c r="F6">
-        <v>2.698</v>
+        <v>15112.602</v>
       </c>
       <c r="G6">
-        <v>3944.9850000000001</v>
+        <v>25828.486</v>
       </c>
       <c r="H6">
-        <v>488757146.83099997</v>
+        <v>226016899.05</v>
       </c>
       <c r="I6">
-        <v>592350.68500000006</v>
+        <v>164968434.156</v>
       </c>
       <c r="J6">
-        <v>913408209.03499997</v>
+        <v>284108596.644</v>
       </c>
       <c r="K6">
-        <v>280587639.02600002</v>
+        <v>2744863612.355</v>
       </c>
       <c r="L6">
-        <v>459873.94199999998</v>
+        <v>2011192360.066</v>
       </c>
       <c r="M6">
-        <v>524835213.40799999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
+        <v>3431657291.078</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
       </c>
       <c r="B7">
-        <v>13422.471</v>
+        <v>151768.319</v>
       </c>
       <c r="C7">
-        <v>9811.2489999999998</v>
+        <v>113666.859</v>
       </c>
       <c r="D7">
-        <v>16881.991999999998</v>
+        <v>187068.869</v>
       </c>
       <c r="E7">
-        <v>3438.3870000000002</v>
+        <v>445375.978</v>
       </c>
       <c r="F7">
-        <v>2521.748</v>
+        <v>331754.807</v>
       </c>
       <c r="G7">
-        <v>4303.1099999999997</v>
+        <v>550660.149</v>
       </c>
       <c r="H7">
-        <v>226030128.45500001</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>165050084.44</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>284369554.95999998</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>457365624.97000003</v>
+        <v>59247059528.709</v>
       </c>
       <c r="L7">
-        <v>335119870.505</v>
+        <v>44174086821.403</v>
       </c>
       <c r="M7">
-        <v>572477073.22800004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
+        <v>73222911917.15401</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Morbidity</t>
+        </is>
       </c>
       <c r="B8">
-        <v>151751.087</v>
+        <v>241875.682</v>
       </c>
       <c r="C8">
-        <v>113659.409</v>
+        <v>149204.086</v>
       </c>
       <c r="D8">
-        <v>187054.89199999999</v>
+        <v>329534.6</v>
       </c>
       <c r="E8">
-        <v>148488.13699999999</v>
+        <v>558997.556</v>
       </c>
       <c r="F8">
-        <v>110847.372</v>
+        <v>369845.622</v>
       </c>
       <c r="G8">
-        <v>183380.128</v>
+        <v>736451.6529999999</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3366813848.775001</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1566765438.098</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>5048917186.167</v>
       </c>
       <c r="K8">
-        <v>19747986835.862999</v>
+        <v>74360052525.998</v>
       </c>
       <c r="L8">
-        <v>14745485651.580999</v>
+        <v>49235349042.58</v>
       </c>
       <c r="M8">
-        <v>24408111325.769001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>20</v>
+        <v>97922219093.34201</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="B9">
-        <v>243123.40100000001</v>
+        <v>300433.673</v>
       </c>
       <c r="C9">
-        <v>149229.51500000001</v>
+        <v>199149.906</v>
       </c>
       <c r="D9">
-        <v>331962.11099999998</v>
+        <v>396527.703</v>
       </c>
       <c r="E9">
-        <v>167773.01699999999</v>
+        <v>1165203.23</v>
       </c>
       <c r="F9">
-        <v>117203.882</v>
+        <v>889124.4959999998</v>
       </c>
       <c r="G9">
-        <v>215026.40299999999</v>
+        <v>1424746.574</v>
       </c>
       <c r="H9">
-        <v>3422257283.177</v>
+        <v>3366813848.775001</v>
       </c>
       <c r="I9">
-        <v>1568467199.059</v>
+        <v>1566765438.098</v>
       </c>
       <c r="J9">
-        <v>5157645704.6709995</v>
+        <v>5048917186.167</v>
       </c>
       <c r="K9">
-        <v>22312322174.602001</v>
+        <v>154977255427.767</v>
       </c>
       <c r="L9">
-        <v>15589645967.136</v>
+        <v>118318486104.804</v>
       </c>
       <c r="M9">
-        <v>28615988388.018002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10">
-        <v>301681.39199999999</v>
-      </c>
-      <c r="C10">
-        <v>199175.33499999999</v>
-      </c>
-      <c r="D10">
-        <v>398955.21399999998</v>
-      </c>
-      <c r="E10">
-        <v>268807.29599999997</v>
-      </c>
-      <c r="F10">
-        <v>203750.361</v>
-      </c>
-      <c r="G10">
-        <v>329742.223</v>
-      </c>
-      <c r="H10">
-        <v>3422257283.177</v>
-      </c>
-      <c r="I10">
-        <v>1568467199.059</v>
-      </c>
-      <c r="J10">
-        <v>5157645704.6709995</v>
-      </c>
-      <c r="K10">
-        <v>35748522658.230003</v>
-      </c>
-      <c r="L10">
-        <v>27103502144.173</v>
-      </c>
-      <c r="M10">
-        <v>43873555679.522003</v>
+        <v>189467622842.368</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_disease.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease.xlsx
@@ -1,21 +1,95 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/Resampling/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3F45A2-0D68-3440-8B92-DB44741E841A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_sup</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_sup</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_sup</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_sup</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +137,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +189,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +223,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +258,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,100 +434,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_sup</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_sup</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_sup</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_sup</t>
-        </is>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>58557.991</v>
+        <v>58557.991000000002</v>
       </c>
       <c r="C2">
         <v>49945.82</v>
       </c>
       <c r="D2">
-        <v>66993.103</v>
+        <v>66993.103000000003</v>
       </c>
       <c r="E2">
         <v>606205.674</v>
       </c>
       <c r="F2">
-        <v>519278.874</v>
+        <v>519278.87400000001</v>
       </c>
       <c r="G2">
-        <v>688294.921</v>
+        <v>688294.92099999997</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,50 +524,48 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>80617202901.769</v>
+        <v>80617202901.768997</v>
       </c>
       <c r="L2">
-        <v>69083137062.224</v>
+        <v>69083137062.223999</v>
       </c>
       <c r="M2">
-        <v>91545403749.026</v>
+        <v>91545403749.026001</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>39415.958</v>
+        <v>39415.957999999999</v>
       </c>
       <c r="C3">
-        <v>24947.584</v>
+        <v>24947.583999999999</v>
       </c>
       <c r="D3">
-        <v>53141.374</v>
+        <v>53141.374000000003</v>
       </c>
       <c r="E3">
-        <v>34353.596</v>
+        <v>34353.595999999998</v>
       </c>
       <c r="F3">
-        <v>21789.613</v>
+        <v>21789.613000000001</v>
       </c>
       <c r="G3">
-        <v>46209.354</v>
+        <v>46209.353999999999</v>
       </c>
       <c r="H3">
-        <v>2196270736.583</v>
+        <v>2196270736.5830002</v>
       </c>
       <c r="I3">
-        <v>1389946392.788</v>
+        <v>1389946392.7880001</v>
       </c>
       <c r="J3">
-        <v>2959480475.341</v>
+        <v>2959480475.3410001</v>
       </c>
       <c r="K3">
-        <v>4570009021.463</v>
+        <v>4570009021.4630003</v>
       </c>
       <c r="L3">
         <v>2893480693.145</v>
@@ -507,57 +574,53 @@
         <v>6145854840.993</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>30761.584</v>
+        <v>30761.583999999999</v>
       </c>
       <c r="C4">
-        <v>782.3390000000001</v>
+        <v>782.33900000000006</v>
       </c>
       <c r="D4">
-        <v>60291.062</v>
+        <v>60291.061999999998</v>
       </c>
       <c r="E4">
-        <v>45968.456</v>
+        <v>45968.455999999998</v>
       </c>
       <c r="F4">
-        <v>1161.487</v>
+        <v>1161.4870000000001</v>
       </c>
       <c r="G4">
-        <v>90086.645</v>
+        <v>90086.645000000004</v>
       </c>
       <c r="H4">
-        <v>455566760.471</v>
+        <v>455566760.47100002</v>
       </c>
       <c r="I4">
         <v>11529871.341</v>
       </c>
       <c r="J4">
-        <v>892262397.48</v>
+        <v>892262397.48000002</v>
       </c>
       <c r="K4">
-        <v>6113416255.102</v>
+        <v>6113416255.1020002</v>
       </c>
       <c r="L4">
-        <v>155325493.918</v>
+        <v>155325493.91800001</v>
       </c>
       <c r="M4">
         <v>11973389123.823</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>6500.221</v>
+        <v>6500.2209999999995</v>
       </c>
       <c r="C5">
         <v>7.931</v>
@@ -578,10 +641,10 @@
         <v>488959452.671</v>
       </c>
       <c r="I5">
-        <v>320739.813</v>
+        <v>320739.81300000002</v>
       </c>
       <c r="J5">
-        <v>913065716.702</v>
+        <v>913065716.70200002</v>
       </c>
       <c r="K5">
         <v>1684704108.369</v>
@@ -590,41 +653,39 @@
         <v>1263674.048</v>
       </c>
       <c r="M5">
-        <v>3148405920.294</v>
+        <v>3148405920.2940001</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
         <v>13429.6</v>
       </c>
       <c r="C6">
-        <v>9799.373</v>
+        <v>9799.3729999999996</v>
       </c>
       <c r="D6">
-        <v>16893.385</v>
+        <v>16893.384999999998</v>
       </c>
       <c r="E6">
         <v>20636.268</v>
       </c>
       <c r="F6">
-        <v>15112.602</v>
+        <v>15112.602000000001</v>
       </c>
       <c r="G6">
-        <v>25828.486</v>
+        <v>25828.486000000001</v>
       </c>
       <c r="H6">
-        <v>226016899.05</v>
+        <v>226016899.05000001</v>
       </c>
       <c r="I6">
-        <v>164968434.156</v>
+        <v>164968434.15599999</v>
       </c>
       <c r="J6">
-        <v>284108596.644</v>
+        <v>284108596.64399999</v>
       </c>
       <c r="K6">
         <v>2744863612.355</v>
@@ -633,32 +694,30 @@
         <v>2011192360.066</v>
       </c>
       <c r="M6">
-        <v>3431657291.078</v>
+        <v>3431657291.0780001</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>151768.319</v>
+        <v>151768.31899999999</v>
       </c>
       <c r="C7">
         <v>113666.859</v>
       </c>
       <c r="D7">
-        <v>187068.869</v>
+        <v>187068.86900000001</v>
       </c>
       <c r="E7">
         <v>445375.978</v>
       </c>
       <c r="F7">
-        <v>331754.807</v>
+        <v>331754.80699999997</v>
       </c>
       <c r="G7">
-        <v>550660.149</v>
+        <v>550660.14899999998</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -676,32 +735,30 @@
         <v>44174086821.403</v>
       </c>
       <c r="M7">
-        <v>73222911917.15401</v>
+        <v>73222911917.154007</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>241875.682</v>
       </c>
       <c r="C8">
-        <v>149204.086</v>
+        <v>149204.08600000001</v>
       </c>
       <c r="D8">
-        <v>329534.6</v>
+        <v>329534.59999999998</v>
       </c>
       <c r="E8">
-        <v>558997.556</v>
+        <v>558997.55599999998</v>
       </c>
       <c r="F8">
-        <v>369845.622</v>
+        <v>369845.62199999997</v>
       </c>
       <c r="G8">
-        <v>736451.6529999999</v>
+        <v>736451.65299999993</v>
       </c>
       <c r="H8">
         <v>3366813848.775001</v>
@@ -710,38 +767,36 @@
         <v>1566765438.098</v>
       </c>
       <c r="J8">
-        <v>5048917186.167</v>
+        <v>5048917186.1669998</v>
       </c>
       <c r="K8">
-        <v>74360052525.998</v>
+        <v>74360052525.998001</v>
       </c>
       <c r="L8">
-        <v>49235349042.58</v>
+        <v>49235349042.580002</v>
       </c>
       <c r="M8">
         <v>97922219093.34201</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>300433.673</v>
+        <v>300433.67300000001</v>
       </c>
       <c r="C9">
-        <v>199149.906</v>
+        <v>199149.90599999999</v>
       </c>
       <c r="D9">
-        <v>396527.703</v>
+        <v>396527.70299999998</v>
       </c>
       <c r="E9">
         <v>1165203.23</v>
       </c>
       <c r="F9">
-        <v>889124.4959999998</v>
+        <v>889124.49599999981</v>
       </c>
       <c r="G9">
         <v>1424746.574</v>
@@ -753,7 +808,7 @@
         <v>1566765438.098</v>
       </c>
       <c r="J9">
-        <v>5048917186.167</v>
+        <v>5048917186.1669998</v>
       </c>
       <c r="K9">
         <v>154977255427.767</v>
@@ -762,7 +817,7 @@
         <v>118318486104.804</v>
       </c>
       <c r="M9">
-        <v>189467622842.368</v>
+        <v>189467622842.36801</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_disease.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease.xlsx
@@ -1,95 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/Resampling/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3F45A2-0D68-3440-8B92-DB44741E841A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_sup</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_sup</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_sup</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_sup</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -189,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -223,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -258,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -434,85 +350,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
       </c>
       <c r="B2">
-        <v>58557.991000000002</v>
+        <v>58557.991</v>
       </c>
       <c r="C2">
         <v>49945.82</v>
       </c>
       <c r="D2">
-        <v>66993.103000000003</v>
+        <v>66993.103</v>
       </c>
       <c r="E2">
         <v>606205.674</v>
       </c>
       <c r="F2">
-        <v>519278.87400000001</v>
+        <v>519278.874</v>
       </c>
       <c r="G2">
-        <v>688294.92099999997</v>
+        <v>688294.921</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -524,103 +455,109 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>80617202901.768997</v>
+        <v>80617202901.769</v>
       </c>
       <c r="L2">
-        <v>69083137062.223999</v>
+        <v>69083137062.224</v>
       </c>
       <c r="M2">
-        <v>91545403749.026001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
+        <v>91545403749.026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
       </c>
       <c r="B3">
-        <v>39415.957999999999</v>
+        <v>39415.958</v>
       </c>
       <c r="C3">
-        <v>24947.583999999999</v>
+        <v>24947.584</v>
       </c>
       <c r="D3">
-        <v>53141.374000000003</v>
+        <v>53141.374</v>
       </c>
       <c r="E3">
-        <v>34353.595999999998</v>
+        <v>34369.655</v>
       </c>
       <c r="F3">
-        <v>21789.613000000001</v>
+        <v>21773.12</v>
       </c>
       <c r="G3">
-        <v>46209.353999999999</v>
+        <v>46213.625</v>
       </c>
       <c r="H3">
-        <v>2196270736.5830002</v>
+        <v>2196270736.583</v>
       </c>
       <c r="I3">
-        <v>1389946392.7880001</v>
+        <v>1389946392.788</v>
       </c>
       <c r="J3">
-        <v>2959480475.3410001</v>
+        <v>2959480475.341</v>
       </c>
       <c r="K3">
-        <v>4570009021.4630003</v>
+        <v>4572585687.843</v>
       </c>
       <c r="L3">
-        <v>2893480693.145</v>
+        <v>2891058688.938</v>
       </c>
       <c r="M3">
-        <v>6145854840.993</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
+        <v>6145437202.348</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
       </c>
       <c r="B4">
-        <v>30761.583999999999</v>
+        <v>30761.584</v>
       </c>
       <c r="C4">
-        <v>782.33900000000006</v>
+        <v>782.3390000000001</v>
       </c>
       <c r="D4">
-        <v>60291.061999999998</v>
+        <v>60291.062</v>
       </c>
       <c r="E4">
-        <v>45968.455999999998</v>
+        <v>45932.085</v>
       </c>
       <c r="F4">
-        <v>1161.4870000000001</v>
+        <v>1161.166</v>
       </c>
       <c r="G4">
-        <v>90086.645000000004</v>
+        <v>89979.177</v>
       </c>
       <c r="H4">
-        <v>455566760.47100002</v>
+        <v>455566760.471</v>
       </c>
       <c r="I4">
         <v>11529871.341</v>
       </c>
       <c r="J4">
-        <v>892262397.48000002</v>
+        <v>892262397.48</v>
       </c>
       <c r="K4">
-        <v>6113416255.1020002</v>
+        <v>6109858905.264</v>
       </c>
       <c r="L4">
-        <v>155325493.91800001</v>
+        <v>155789191.443</v>
       </c>
       <c r="M4">
-        <v>11973389123.823</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
+        <v>11959404804.633</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
       </c>
       <c r="B5">
-        <v>6500.2209999999995</v>
+        <v>6500.221</v>
       </c>
       <c r="C5">
         <v>7.931</v>
@@ -629,95 +566,99 @@
         <v>12139.91</v>
       </c>
       <c r="E5">
-        <v>12663.258</v>
+        <v>12659.951</v>
       </c>
       <c r="F5">
-        <v>27.113</v>
+        <v>24.496</v>
       </c>
       <c r="G5">
-        <v>23667.019</v>
+        <v>23695.215</v>
       </c>
       <c r="H5">
         <v>488959452.671</v>
       </c>
       <c r="I5">
-        <v>320739.81300000002</v>
+        <v>320739.813</v>
       </c>
       <c r="J5">
-        <v>913065716.70200002</v>
+        <v>913065716.702</v>
       </c>
       <c r="K5">
-        <v>1684704108.369</v>
+        <v>1683971856.375</v>
       </c>
       <c r="L5">
-        <v>1263674.048</v>
+        <v>966847.243</v>
       </c>
       <c r="M5">
-        <v>3148405920.2940001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
+        <v>3151226189.343</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
       </c>
       <c r="B6">
         <v>13429.6</v>
       </c>
       <c r="C6">
-        <v>9799.3729999999996</v>
+        <v>9799.373</v>
       </c>
       <c r="D6">
-        <v>16893.384999999998</v>
+        <v>16893.385</v>
       </c>
       <c r="E6">
-        <v>20636.268</v>
+        <v>20636.229</v>
       </c>
       <c r="F6">
-        <v>15112.602000000001</v>
+        <v>15114.386</v>
       </c>
       <c r="G6">
-        <v>25828.486000000001</v>
+        <v>25832.584</v>
       </c>
       <c r="H6">
-        <v>226016899.05000001</v>
+        <v>226016899.05</v>
       </c>
       <c r="I6">
-        <v>164968434.15599999</v>
+        <v>164968434.156</v>
       </c>
       <c r="J6">
-        <v>284108596.64399999</v>
+        <v>284108596.644</v>
       </c>
       <c r="K6">
-        <v>2744863612.355</v>
+        <v>2744757090.679</v>
       </c>
       <c r="L6">
-        <v>2011192360.066</v>
+        <v>2011358058.182</v>
       </c>
       <c r="M6">
-        <v>3431657291.0780001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
+        <v>3432180413.355</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
       </c>
       <c r="B7">
-        <v>151768.31899999999</v>
+        <v>151768.319</v>
       </c>
       <c r="C7">
         <v>113666.859</v>
       </c>
       <c r="D7">
-        <v>187068.86900000001</v>
+        <v>187068.869</v>
       </c>
       <c r="E7">
-        <v>445375.978</v>
+        <v>445289.766</v>
       </c>
       <c r="F7">
-        <v>331754.80699999997</v>
+        <v>332233.623</v>
       </c>
       <c r="G7">
-        <v>550660.14899999998</v>
+        <v>551090.9889999999</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -729,36 +670,38 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>59247059528.709</v>
+        <v>59223474939.172</v>
       </c>
       <c r="L7">
-        <v>44174086821.403</v>
+        <v>44206490946.8</v>
       </c>
       <c r="M7">
-        <v>73222911917.154007</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
+        <v>73276579050.64301</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Morbidity</t>
+        </is>
       </c>
       <c r="B8">
         <v>241875.682</v>
       </c>
       <c r="C8">
-        <v>149204.08600000001</v>
+        <v>149204.086</v>
       </c>
       <c r="D8">
-        <v>329534.59999999998</v>
+        <v>329534.6</v>
       </c>
       <c r="E8">
-        <v>558997.55599999998</v>
+        <v>558887.686</v>
       </c>
       <c r="F8">
-        <v>369845.62199999997</v>
+        <v>370306.791</v>
       </c>
       <c r="G8">
-        <v>736451.65299999993</v>
+        <v>736811.59</v>
       </c>
       <c r="H8">
         <v>3366813848.775001</v>
@@ -767,39 +710,41 @@
         <v>1566765438.098</v>
       </c>
       <c r="J8">
-        <v>5048917186.1669998</v>
+        <v>5048917186.167</v>
       </c>
       <c r="K8">
-        <v>74360052525.998001</v>
+        <v>74334648479.33299</v>
       </c>
       <c r="L8">
-        <v>49235349042.580002</v>
+        <v>49265663732.606</v>
       </c>
       <c r="M8">
-        <v>97922219093.34201</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>20</v>
+        <v>97964827660.32201</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="B9">
-        <v>300433.67300000001</v>
+        <v>300433.673</v>
       </c>
       <c r="C9">
-        <v>199149.90599999999</v>
+        <v>199149.906</v>
       </c>
       <c r="D9">
-        <v>396527.70299999998</v>
+        <v>396527.703</v>
       </c>
       <c r="E9">
-        <v>1165203.23</v>
+        <v>1165093.36</v>
       </c>
       <c r="F9">
-        <v>889124.49599999981</v>
+        <v>889585.6650000002</v>
       </c>
       <c r="G9">
-        <v>1424746.574</v>
+        <v>1425106.511</v>
       </c>
       <c r="H9">
         <v>3366813848.775001</v>
@@ -808,16 +753,16 @@
         <v>1566765438.098</v>
       </c>
       <c r="J9">
-        <v>5048917186.1669998</v>
+        <v>5048917186.167</v>
       </c>
       <c r="K9">
-        <v>154977255427.767</v>
+        <v>154951851381.102</v>
       </c>
       <c r="L9">
-        <v>118318486104.804</v>
+        <v>118348800794.83</v>
       </c>
       <c r="M9">
-        <v>189467622842.36801</v>
+        <v>189510231409.348</v>
       </c>
     </row>
   </sheetData>
